--- a/diseases/d169/2015-2019.xlsx
+++ b/diseases/d169/2015-2019.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1069,6 +1079,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1214,6 +1229,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1362,6 +1382,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1507,6 +1532,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1655,6 +1685,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1803,6 +1838,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1948,6 +1988,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2096,6 +2141,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2244,6 +2294,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2389,6 +2444,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2537,6 +2597,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2685,6 +2750,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2830,6 +2900,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2978,6 +3053,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3126,6 +3206,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3271,6 +3356,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3419,6 +3509,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3567,6 +3662,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3712,6 +3812,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3860,6 +3965,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4008,6 +4118,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4153,6 +4268,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4301,6 +4421,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4449,6 +4574,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4594,6 +4724,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4742,6 +4877,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4890,6 +5030,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5035,6 +5180,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5183,6 +5333,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5331,6 +5486,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5476,6 +5636,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5624,6 +5789,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5772,6 +5942,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5917,6 +6092,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6065,6 +6245,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6213,6 +6398,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6358,6 +6548,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6506,6 +6701,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6651,6 +6851,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6799,6 +7004,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6944,6 +7154,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7092,6 +7307,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7237,6 +7457,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7385,6 +7610,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7533,6 +7763,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7678,6 +7913,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7826,6 +8066,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7974,6 +8219,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8119,6 +8369,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8267,6 +8522,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8415,6 +8675,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8560,6 +8825,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8708,6 +8978,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8856,6 +9131,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9001,6 +9281,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9149,6 +9434,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9294,6 +9584,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9442,6 +9737,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9587,6 +9887,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9735,6 +10040,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9883,6 +10193,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10028,6 +10343,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10176,6 +10496,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10324,6 +10649,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10469,6 +10799,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12587,6 +12922,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12732,6 +13072,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12880,6 +13225,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14604,6 +14954,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14749,6 +15104,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14897,6 +15257,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16621,6 +16986,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16766,6 +17136,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16914,6 +17289,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19032,6 +19412,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19177,6 +19562,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19325,6 +19715,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21049,6 +21444,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21194,6 +21594,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21342,6 +21747,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23066,6 +23476,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23211,6 +23626,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23359,6 +23779,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25477,6 +25902,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25622,6 +26052,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25770,6 +26205,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27494,6 +27934,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27639,6 +28084,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29363,6 +29813,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29508,6 +29963,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30050,6 +30510,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31774,6 +32239,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31919,6 +32389,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33643,6 +34118,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33788,6 +34268,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33936,6 +34421,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36054,6 +36544,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36199,6 +36694,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36347,6 +36847,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38071,6 +38576,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38216,6 +38726,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38364,6 +38879,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO219" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40088,6 +40608,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO228" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40233,6 +40758,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO229" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40381,6 +40911,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42105,6 +42640,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO239" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42250,6 +42790,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44368,6 +44913,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO251" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44513,6 +45063,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO252" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44661,6 +45216,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO253" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46385,6 +46945,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO262" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46530,6 +47095,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO263" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46678,6 +47248,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO264" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48402,6 +48977,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO273" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48547,6 +49127,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO274" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49089,6 +49674,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO277" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50813,6 +51403,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO286" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50958,6 +51553,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO287" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51106,6 +51706,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO288" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52830,6 +53435,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA297" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO297" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52975,6 +53585,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA298" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO298" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53123,6 +53738,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA299" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO299" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55241,6 +55861,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA310" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO310" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55386,6 +56011,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA311" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO311" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55534,6 +56164,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA312" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO312" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57258,6 +57893,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA321" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO321" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57403,6 +58043,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA322" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO322" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59127,6 +59772,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA331" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO331" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59272,6 +59922,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA332" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO332" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61390,6 +62045,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA343" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO343" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61535,6 +62195,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA344" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO344" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61683,6 +62348,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA345" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO345" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63407,6 +64077,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA354" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO354" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63552,6 +64227,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA355" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO355" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65276,6 +65956,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA364" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO364" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65421,6 +66106,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA365" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO365" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65569,6 +66259,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA366" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO366" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67687,6 +68382,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA377" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO377" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67832,6 +68532,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA378" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO378" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67980,6 +68685,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA379" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO379" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69704,6 +70414,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA388" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO388" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69849,6 +70564,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA389" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO389" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69997,6 +70717,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA390" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO390" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71721,6 +72446,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA399" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO399" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71866,6 +72596,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA400" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO400" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -72014,6 +72749,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA401" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO401" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -74132,6 +74872,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA412" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO412" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -74277,6 +75022,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA413" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO413" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -74425,6 +75175,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA414" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO414" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -76149,6 +76904,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA423" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO423" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -76294,6 +77054,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA424" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO424" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -76442,6 +77207,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA425" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO425" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -78166,6 +78936,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA434" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO434" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -78311,6 +79086,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA435" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO435" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -78853,6 +79633,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA438" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO438" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -80577,6 +81362,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA447" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO447" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -80722,6 +81512,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA448" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO448" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -80870,6 +81665,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA449" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO449" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -82594,6 +83394,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA458" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO458" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -82739,6 +83544,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA459" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO459" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -82887,6 +83697,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA460" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO460" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -84611,6 +85426,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA469" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO469" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -84754,6 +85574,11 @@
       <c r="S470" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA470" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO470" t="inlineStr">
